--- a/artfynd/A 64874-2021 artfynd.xlsx
+++ b/artfynd/A 64874-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64874-2021 artfynd.xlsx
+++ b/artfynd/A 64874-2021 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7254083</v>
+        <v>402708</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,21 +705,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rockhammar, Lillån, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526202.3298154483</v>
+        <v>526206</v>
       </c>
       <c r="R2" t="n">
-        <v>6599755.107577454</v>
+        <v>6599779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-04-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-04-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,10 +763,15 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -794,19 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52967937</v>
+        <v>7254083</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,14 +817,10 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526195.3724533654</v>
+        <v>526202</v>
       </c>
       <c r="R3" t="n">
-        <v>6599732.741915029</v>
+        <v>6599755</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-04-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-04-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,19 +891,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52967938</v>
+        <v>52967937</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,7 +921,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,16 +929,17 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rockhammar, Lillån, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526335.2605146188</v>
+        <v>526195</v>
       </c>
       <c r="R4" t="n">
-        <v>6599491.772168492</v>
+        <v>6599733</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,19 +969,9 @@
           <t>2015-04-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-04-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64855357</v>
+        <v>52967938</v>
       </c>
       <c r="B5" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1074,19 +1029,24 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rockhammar, lillån, Vstm</t>
+          <t>Rockhammar, Lillån, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526280.2311730583</v>
+        <v>526335</v>
       </c>
       <c r="R5" t="n">
-        <v>6599586.24032289</v>
+        <v>6599492</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-04-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-04-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,26 +1099,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann, Claes Urban Eliasson, Berit Ragné</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>70699687</v>
+        <v>64855357</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1190,12 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526341.3932113943</v>
+        <v>526280</v>
       </c>
       <c r="R6" t="n">
-        <v>6599486.74269776</v>
+        <v>6599586</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,27 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-04-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-04-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>växtplas gallrat, ej uppmärkt</t>
+          <t>2017-04-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,26 +1200,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Herbert Kaufmann, Claes Urban Eliasson, Berit Ragné</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70699686</v>
+        <v>70699680</v>
       </c>
       <c r="B7" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1316,7 +1237,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1330,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526278.1952920848</v>
+        <v>526300</v>
       </c>
       <c r="R7" t="n">
-        <v>6599586.733322615</v>
+        <v>6599580</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,24 +1284,14 @@
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>vid bäcken, gallrat skog, växtplats ej märkt</t>
+          <t>ny växtplas i sluttning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,16 +1321,11 @@
         <v>70699681</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1456,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526302.0929768019</v>
+        <v>526302</v>
       </c>
       <c r="R8" t="n">
-        <v>6599584.364279477</v>
+        <v>6599584</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,19 +1395,9 @@
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-04-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1533,19 +1429,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>70699680</v>
+        <v>70699684</v>
       </c>
       <c r="B9" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1568,7 +1459,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1582,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526300.0890241094</v>
+        <v>526194</v>
       </c>
       <c r="R9" t="n">
-        <v>6599580.292416389</v>
+        <v>6599705</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1615,24 +1506,14 @@
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ny växtplas i sluttning</t>
+          <t>markering längs ån</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,19 +1540,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70699684</v>
+        <v>70699686</v>
       </c>
       <c r="B10" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1694,7 +1570,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1708,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526194.0426176022</v>
+        <v>526278</v>
       </c>
       <c r="R10" t="n">
-        <v>6599704.835990899</v>
+        <v>6599587</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1741,24 +1617,14 @@
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>markering längs ån</t>
+          <t>vid bäcken, gallrat skog, växtplats ej märkt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,19 +1651,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76936137</v>
+        <v>70699687</v>
       </c>
       <c r="B11" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1820,19 +1681,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rockhammar Lillån, Vstm</t>
+          <t>Rockhammar, lillån, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526277.2181186661</v>
+        <v>526341</v>
       </c>
       <c r="R11" t="n">
-        <v>6599581.146959756</v>
+        <v>6599487</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1859,22 +1725,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-04-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-04-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>växtplas gallrat, ej uppmärkt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1901,19 +1762,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108541391</v>
+        <v>76936137</v>
       </c>
       <c r="B12" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1934,20 +1790,21 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rockhammar, Lillån, Vstm</t>
+          <t>Rockhammar Lillån, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526275.1113419739</v>
+        <v>526277</v>
       </c>
       <c r="R12" t="n">
-        <v>6599591.784064419</v>
+        <v>6599581</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1974,31 +1831,20 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +1856,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann, Kari Storvestre, Emil Pagstedt Andersson</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 64874-2021 artfynd.xlsx
+++ b/artfynd/A 64874-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/402708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7254083</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/52967937</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/52967938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64855357</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70699680</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70699681</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70699684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70699686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70699687</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,8 +1915,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76936137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>